--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260812.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,291,000</t>
+          <t>10,742,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>10,742,000</t>
+          <t>2,291,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>17,902,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
